--- a/AdvCompProS01-268.xlsx
+++ b/AdvCompProS01-268.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rach-WED\Desktop\adv-fullstack-268\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38CD628-FB02-431C-9831-F9379AEA59AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAD91D8-D0D9-403A-B4F8-EE830650FF19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="54">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าพระนครเหนือ</t>
   </si>
@@ -577,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
@@ -612,6 +612,18 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -624,20 +636,11 @@
     <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -987,137 +990,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
     </row>
     <row r="4" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
     </row>
     <row r="5" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:20" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1133,24 +1136,24 @@
       <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
     </row>
     <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1248,7 +1251,9 @@
       <c r="M10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="7"/>
+      <c r="N10" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -1290,7 +1295,9 @@
       <c r="M11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="7"/>
+      <c r="N11" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
@@ -1332,7 +1339,9 @@
       <c r="M12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="7"/>
+      <c r="N12" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
@@ -1374,7 +1383,9 @@
       <c r="M13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="7"/>
+      <c r="N13" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -1416,7 +1427,9 @@
       <c r="M14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -1458,7 +1471,9 @@
       <c r="M15" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N15" s="7"/>
+      <c r="N15" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -1500,7 +1515,9 @@
       <c r="M16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="7"/>
+      <c r="N16" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
@@ -1542,7 +1559,9 @@
       <c r="M17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="7"/>
+      <c r="N17" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -1584,7 +1603,9 @@
       <c r="M18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="7"/>
+      <c r="N18" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
@@ -1626,7 +1647,9 @@
       <c r="M19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="7"/>
+      <c r="N19" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
@@ -1668,7 +1691,9 @@
       <c r="M20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="7"/>
+      <c r="N20" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
@@ -1710,7 +1735,9 @@
       <c r="M21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="7"/>
+      <c r="N21" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
@@ -1752,7 +1779,9 @@
       <c r="M22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="7"/>
+      <c r="N22" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -1794,7 +1823,9 @@
       <c r="M23" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="7"/>
+      <c r="N23" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
@@ -1836,7 +1867,9 @@
       <c r="M24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="7"/>
+      <c r="N24" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
@@ -1878,7 +1911,9 @@
       <c r="M25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="7"/>
+      <c r="N25" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
@@ -1887,36 +1922,36 @@
       <c r="T25" s="7"/>
     </row>
     <row r="26" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="20" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
     </row>
     <row r="27" spans="1:20" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
     </row>
     <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="C29" s="11" t="s">
@@ -1940,20 +1975,23 @@
       <c r="M29" s="10" t="s">
         <v>51</v>
       </c>
+      <c r="N29" s="21" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A26:D27"/>
-    <mergeCell ref="E8:T8"/>
-    <mergeCell ref="E26:T26"/>
-    <mergeCell ref="F4:T4"/>
-    <mergeCell ref="F5:T5"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E6"/>
     <mergeCell ref="I1:T1"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="E8:T8"/>
+    <mergeCell ref="E26:T26"/>
+    <mergeCell ref="F4:T4"/>
+    <mergeCell ref="F5:T5"/>
   </mergeCells>
   <pageMargins left="0.437" right="8.2699999999999996E-2" top="0.35039999999999999" bottom="7.8700000000000006E-2" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>

--- a/AdvCompProS01-268.xlsx
+++ b/AdvCompProS01-268.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rach-WED\Desktop\adv-fullstack-268\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAD91D8-D0D9-403A-B4F8-EE830650FF19}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081B2173-FBFE-413A-9318-2ABC85FB23B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -612,6 +612,27 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -620,27 +641,6 @@
     </xf>
     <xf numFmtId="49" fontId="17" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -990,137 +990,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="20" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
     </row>
     <row r="3" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
     </row>
     <row r="4" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="15" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
     </row>
     <row r="5" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:20" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1136,24 +1136,24 @@
       <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
     </row>
     <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -1604,7 +1604,7 @@
         <v>51</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -1922,36 +1922,36 @@
       <c r="T25" s="7"/>
     </row>
     <row r="26" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="14" t="s">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
     </row>
     <row r="27" spans="1:20" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
     </row>
     <row r="29" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
       <c r="C29" s="11" t="s">
@@ -1975,23 +1975,23 @@
       <c r="M29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="21" t="s">
+      <c r="N29" s="12" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="E8:T8"/>
+    <mergeCell ref="E26:T26"/>
+    <mergeCell ref="F4:T4"/>
+    <mergeCell ref="F5:T5"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:T2"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E6"/>
     <mergeCell ref="I1:T1"/>
-    <mergeCell ref="A26:D27"/>
-    <mergeCell ref="E8:T8"/>
-    <mergeCell ref="E26:T26"/>
-    <mergeCell ref="F4:T4"/>
-    <mergeCell ref="F5:T5"/>
   </mergeCells>
   <pageMargins left="0.437" right="8.2699999999999996E-2" top="0.35039999999999999" bottom="7.8700000000000006E-2" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
